--- a/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,4</t>
+          <t>2,17; 9,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,03</t>
+          <t>-5,35; 3,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,25</t>
+          <t>-2,23; 7,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 15,19</t>
+          <t>6,44; 15,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 50,49</t>
+          <t>9,94; 51,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 6,75</t>
+          <t>-10,68; 7,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 20,86</t>
+          <t>-5,5; 20,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,02; 68,79</t>
+          <t>21,16; 66,1</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 7,21</t>
+          <t>0,08; 6,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,35</t>
+          <t>2,28; 9,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,79</t>
+          <t>4,43; 11,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 29,73</t>
+          <t>-0,89; 33,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 35,76</t>
+          <t>0,42; 34,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 17,69</t>
+          <t>4,14; 18,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,41; 29,86</t>
+          <t>10,21; 29,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 150,06</t>
+          <t>-3,99; 158,88</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,37</t>
+          <t>-3,72; 8,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 12,96</t>
+          <t>-2,6; 12,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 11,52</t>
+          <t>-4,66; 10,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 4,8</t>
+          <t>-6,3; 5,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 45,07</t>
+          <t>-13,35; 40,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 27,37</t>
+          <t>-4,86; 25,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 26,32</t>
+          <t>-8,94; 24,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 27,73</t>
+          <t>-25,84; 30,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,7</t>
+          <t>1,95; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,83</t>
+          <t>-0,44; 5,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,17</t>
+          <t>2,54; 8,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 26,11</t>
+          <t>2,33; 26,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 32,93</t>
+          <t>8,87; 31,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,61</t>
+          <t>-0,82; 10,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 20,06</t>
+          <t>5,91; 20,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 117,41</t>
+          <t>9,98; 116,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,77</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,51</t>
+          <t>1,98; 9,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 3,43</t>
+          <t>-5,84; 3,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 7,3</t>
+          <t>-2,34; 7,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 15,34</t>
+          <t>6,88; 15,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 51,93</t>
+          <t>8,98; 51,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 7,69</t>
+          <t>-11,72; 7,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 20,36</t>
+          <t>-5,46; 21,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 66,1</t>
+          <t>23,22; 71,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,99</t>
+          <t>0,46; 7,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,63</t>
+          <t>2,07; 9,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,57</t>
+          <t>4,11; 11,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 33,55</t>
+          <t>-1,75; 4,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 34,27</t>
+          <t>2,53; 35,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 18,51</t>
+          <t>3,62; 18,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 29,18</t>
+          <t>9,49; 29,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 158,88</t>
+          <t>-6,61; 20,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,78%</t>
+          <t>-3,02%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 8,96</t>
+          <t>-3,2; 10,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 12,67</t>
+          <t>-2,55; 12,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 10,71</t>
+          <t>-4,94; 10,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 5,05</t>
+          <t>-6,32; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 40,94</t>
+          <t>-11,97; 47,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 25,95</t>
+          <t>-4,56; 26,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 24,92</t>
+          <t>-9,73; 23,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 30,18</t>
+          <t>-24,71; 22,46</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,62</t>
+          <t>2,08; 6,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,02</t>
+          <t>-0,21; 4,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,07</t>
+          <t>2,45; 8,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 26,03</t>
+          <t>1,37; 6,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 31,64</t>
+          <t>8,81; 32,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 10,09</t>
+          <t>-0,42; 9,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 20,22</t>
+          <t>5,79; 20,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 116,57</t>
+          <t>5,5; 27,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
